--- a/output/laminas_comunales/comunal_s_isapre_a_2024_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_los_lagos.xlsx
@@ -375,256 +375,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C2">
-        <v>28383</v>
+        <v>24.37583124295022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C3">
-        <v>18044</v>
+        <v>10.31569668141999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C4">
-        <v>14479</v>
+        <v>10.17939749520478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C5">
-        <v>5617</v>
+        <v>10.12178378474761</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C6">
-        <v>2780</v>
+        <v>9.837855323278477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C7">
-        <v>2433</v>
+        <v>8.422634922174272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C8">
-        <v>1737</v>
+        <v>7.052607397197336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C9">
-        <v>1434</v>
+        <v>6.560114503816794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C10">
-        <v>1228</v>
+        <v>5.803757828810021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C11">
-        <v>993</v>
+        <v>5.590185020282973</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C12">
-        <v>824</v>
+        <v>5.150872230080151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C13">
-        <v>792</v>
+        <v>4.618058429198046</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C14">
-        <v>703</v>
+        <v>4.577505490694717</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C15">
-        <v>567</v>
+        <v>4.470475735118336</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C16">
-        <v>565</v>
+        <v>4.44513329200248</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C17">
-        <v>560</v>
+        <v>4.271219393644814</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C18">
-        <v>558</v>
+        <v>4.18027433050294</v>
       </c>
     </row>
     <row r="19">
@@ -639,187 +639,187 @@
         </is>
       </c>
       <c r="C19">
-        <v>542</v>
+        <v>4.088097752300498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C20">
-        <v>448</v>
+        <v>3.865640833176956</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C21">
-        <v>437</v>
+        <v>3.739118965972039</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C22">
-        <v>420</v>
+        <v>3.225806451612903</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="C23">
-        <v>275</v>
+        <v>3.067708713753561</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C24">
-        <v>259</v>
+        <v>3.048041986273718</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C25">
-        <v>256</v>
+        <v>2.89870076090895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C26">
-        <v>187</v>
+        <v>2.794260438019204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C27">
-        <v>151</v>
+        <v>2.676384491307724</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C28">
-        <v>146</v>
+        <v>2.605956471935853</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C29">
-        <v>102</v>
+        <v>2.560532219385782</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C30">
-        <v>91</v>
+        <v>2.362835402482979</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C31">
-        <v>59</v>
+        <v>1.184944237918216</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
